--- a/livrables/tbase_par_bande_rectifies.xlsx
+++ b/livrables/tbase_par_bande_rectifies.xlsx
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C61" t="n">
